--- a/tests/fixtures/21_monthly_budget/21_monthly_budget_pattern-from-draft.xlsx
+++ b/tests/fixtures/21_monthly_budget/21_monthly_budget_pattern-from-draft.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -461,48 +461,41 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pattern.version</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>config:</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>read.direction</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>LR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>col_proj_cost</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Projected Cost</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -512,7 +505,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>col_actual_cost</t>
+          <t>col_proj_cost</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -522,7 +515,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Actual Cost</t>
+          <t>Projected Cost</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -536,7 +529,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>col_difference</t>
+          <t>col_actual_cost</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -546,35 +539,35 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>Actual Cost</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>budget.title</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>col_difference</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -584,12 +577,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>income.proj_total</t>
+          <t>budget.title</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -608,7 +601,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>income.actual_total</t>
+          <t>income.proj_total</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -632,7 +625,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>balance.projected</t>
+          <t>income.actual_total</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -656,7 +649,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>balance.actual</t>
+          <t>balance.projected</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -680,7 +673,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>balance.difference</t>
+          <t>balance.actual</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -704,12 +697,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>expense.category</t>
+          <t>balance.difference</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -728,12 +721,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>expense.projected</t>
+          <t>expense.category</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -752,7 +745,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>expense.actual</t>
+          <t>expense.projected</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -776,7 +769,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>expense.difference</t>
+          <t>expense.actual</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -793,42 +786,50 @@
       <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>expense.difference</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>cell:B2</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>budget.title</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>cell:J4</t>
+          <t>cell:B2</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>balance.projected</t>
+          <t>budget.title</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -839,12 +840,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>cell:E6</t>
+          <t>cell:J4</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>income.proj_total</t>
+          <t>balance.projected</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -855,12 +856,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>cell:J6</t>
+          <t>cell:E6</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>balance.actual</t>
+          <t>income.proj_total</t>
         </is>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -871,12 +872,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>cell:J8</t>
+          <t>cell:J6</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>balance.difference</t>
+          <t>balance.actual</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -887,12 +888,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>cell:E10</t>
+          <t>cell:J8</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>income.actual_total</t>
+          <t>balance.difference</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -901,84 +902,100 @@
       <c r="F21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>cell:E10</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>income.actual_total</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>col_proj_cost</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>col_actual_cost</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>col_difference</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>expense.category</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>expense.projected</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>expense.actual</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>expense.difference</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
